--- a/Project-FTO/QF.xlsx
+++ b/Project-FTO/QF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtinoco2\Downloads\Failures-PMI\Project-FTO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Downloads\Failures-PMI\Project-FTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC3AA0BD-731B-4593-BCAA-BD0C95567999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E56DF18-9DDC-4383-8058-630B4B03B743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="0" windowWidth="20784" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
   <si>
     <t>INITIATOR</t>
   </si>
@@ -28,12 +28,6 @@
     <t>WORKCENTER</t>
   </si>
   <si>
-    <t>EVENT DESCRIPTION</t>
-  </si>
-  <si>
-    <t>IMMEDIATE ACTION/CORRECTION</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
@@ -43,136 +37,31 @@
     <t>KDF 07</t>
   </si>
   <si>
-    <t>Se detecta inestabilidad en el RTD, provocando que tengamos que trabajar en modo manual para estabilizar la máquina, asi como bajar los parámetros de rodillo V3/V2, y V1/ VKDF, Tambien se detecta que no llevan una sincronizacion kdf y AMCS</t>
-  </si>
-  <si>
-    <t>Se levanta QRP</t>
-  </si>
-  <si>
     <t>Marcos.Roblero@pmi.com</t>
   </si>
   <si>
     <t>KDF 08</t>
   </si>
   <si>
-    <t>se detecta que la linea de goma de refuerzo no la lleva y la camara no lo detecto</t>
-  </si>
-  <si>
-    <t>se para maquina y se separan cajas</t>
-  </si>
-  <si>
     <t>JulioCesar.Martinez@pmi.com</t>
   </si>
   <si>
-    <t>camara de gomas sin funcionar</t>
-  </si>
-  <si>
-    <t>se reporta a electricos</t>
-  </si>
-  <si>
-    <t>amcs 1 se descalibra</t>
-  </si>
-  <si>
-    <t>calibracion inmediata e revision por el especialista</t>
-  </si>
-  <si>
     <t>Guadalupe.Dominguez@pmi.com</t>
   </si>
   <si>
     <t>KDF 17</t>
   </si>
   <si>
-    <t>codigo de capsula incorrecto a la especificacion</t>
-  </si>
-  <si>
-    <t>correccion de material</t>
-  </si>
-  <si>
     <t>Victor.Zuniga@pmi.com</t>
   </si>
   <si>
     <t>KDF 10 (MULF 1)</t>
   </si>
   <si>
-    <t>filtro con mal corte</t>
-  </si>
-  <si>
-    <t>se levanta qf y se separa producto</t>
-  </si>
-  <si>
-    <t>Digiperf fuera de servicio</t>
-  </si>
-  <si>
-    <t>QF</t>
-  </si>
-  <si>
-    <t>se detecta que la linea de goma de refuerzo no la lleva y la camara no lo detecto y se abre el filtro</t>
-  </si>
-  <si>
-    <t>circunferencia variable</t>
-  </si>
-  <si>
-    <t>Amcs se descalibra</t>
-  </si>
-  <si>
-    <t>Calibración equipo</t>
-  </si>
-  <si>
-    <t>circunferencia variable en semifiltro y con un pequeño golpe provocando mal enrollado en kdf 10</t>
-  </si>
-  <si>
-    <t>se levanta qf y se separa producto a local</t>
-  </si>
-  <si>
     <t>JoseRaul.Rodriguez@pmi.com</t>
   </si>
   <si>
-    <t>orificio en punta de barra de filtro</t>
-  </si>
-  <si>
-    <t>SE AVISA A CALIDAD</t>
-  </si>
-  <si>
-    <t>abrazadera dentro de una caja  vacia de filtros</t>
-  </si>
-  <si>
-    <t>se retira de la caja y se guarda</t>
-  </si>
-  <si>
-    <t>mane proveedor capsulas fragiles</t>
-  </si>
-  <si>
-    <t>solo q f , limpieza a residuos en hci</t>
-  </si>
-  <si>
-    <t>semifiltro 144 con media luna provoca mal enrollado</t>
-  </si>
-  <si>
-    <t>filtro de 144 mal enrrollado</t>
-  </si>
-  <si>
-    <t>se avisa a linea de estructura</t>
-  </si>
-  <si>
     <t>Nicolas.Solorzano@pmi.com</t>
-  </si>
-  <si>
-    <t>sin conexión SPA</t>
-  </si>
-  <si>
-    <t>REPORTE A DEPARTAMENTO CORRESPONDIENTE</t>
-  </si>
-  <si>
-    <t>numero de recurso no coincidi con espec y si deja asignar</t>
-  </si>
-  <si>
-    <t>REPORTE</t>
-  </si>
-  <si>
-    <t>Applied filters:
-DETECTION DATE AND DETECTION TIME LOCAL is on or after 1/1/2026 12:00:00 AM and is before 3/14/2026 12:00:00 AM
-BUSINESS UNIT is Filter Making
-CellGroup is Capsulas</t>
   </si>
 </sst>
 </file>
@@ -205,11 +94,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -220,7 +115,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -239,7 +134,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -555,13 +450,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,339 +467,214 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="C2" s="2">
+        <v>46067.182638888888</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46073.363888888889</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46074.063194444447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46074.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2">
-        <v>46067.182638888888</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C6" s="2">
+        <v>46078.484722222223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C7" s="2">
+        <v>46078.573611111111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46079.317361111112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46079.43472222222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46079.450694444444</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46081.99722222222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46084.352777777778</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2">
-        <v>46073.363888888889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46086.762499999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46087.324999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46087.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46088.219444444447</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46092.23541666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46092.30972222222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2">
-        <v>46074.063194444447</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46074.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46078.484722222223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46078.573611111111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2">
-        <v>46079.317361111112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+      <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46079.43472222222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2">
-        <v>46079.450694444444</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2">
-        <v>46081.99722222222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46084.352777777778</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2">
-        <v>46086.762499999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2">
-        <v>46087.324999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="2">
-        <v>46087.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46088.219444444447</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="2">
-        <v>46092.23541666667</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="2">
-        <v>46092.30972222222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="C19" s="2">
         <v>46092.561111111114</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="2">
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2">
         <v>46092.938888888886</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
